--- a/engine/publish_queue/SWDY/SWDY_Valuation_Model_13092026_public.xlsx
+++ b/engine/publish_queue/SWDY/SWDY_Valuation_Model_13092026_public.xlsx
@@ -2985,19 +2985,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>66.63013824272224</v>
+        <v>81.01576402177247</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>83.24518221853894</v>
+        <v>84.499937518341</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>99.66193933569537</v>
+        <v>87.94253027526975</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>108.80678833518</v>
+        <v>89.86020443613874</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>116.4752701701724</v>
+        <v>91.46828451147806</v>
       </c>
       <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>79.09245631047411</v>
+        <v>77.86463479154189</v>
       </c>
     </row>
     <row r="19">

--- a/engine/publish_queue/SWDY/SWDY_Valuation_Model_13092026_public.xlsx
+++ b/engine/publish_queue/SWDY/SWDY_Valuation_Model_13092026_public.xlsx
@@ -2955,20 +2955,20 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Working capital / revenue  (17.0% / 18.5% / 19.9% / 21.5% / 23.0%)</t>
+          <t>Working capital / revenue  (17.0% / 18.5% / 19.7% / 21.5% / 23.0%)</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
         <v>97.75178736220548</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>92.24096877403932</v>
+        <v>92.24096877403929</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>87.09753809175092</v>
+        <v>87.94253027526975</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>81.21933159770705</v>
+        <v>81.21933159770703</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>75.70851300954091</v>
